--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260909_220413.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260909_220413.xlsx
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260909_220413.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260909_220413.xlsx
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
